--- a/excel/SMART6.0智能锁大屏_测试用例.xlsx
+++ b/excel/SMART6.0智能锁大屏_测试用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="14055"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="330">
   <si>
     <t>用例编号</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>高</t>
-  </si>
-  <si>
-    <t>pass</t>
   </si>
   <si>
     <t>TC_DS_002</t>
@@ -2266,1480 +2263,1285 @@
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" ht="54" customHeight="1" spans="1:7">
       <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="4" ht="40.5" customHeight="1" spans="1:7">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" ht="40.5" customHeight="1" spans="1:7">
       <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1" spans="1:7">
       <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="7" ht="40.5" customHeight="1" spans="1:7">
       <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="8" ht="40.5" customHeight="1" spans="1:7">
       <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="9" ht="27" customHeight="1" spans="1:7">
       <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1" spans="1:7">
       <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="11" ht="54" customHeight="1" spans="1:7">
       <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="12" ht="40.5" customHeight="1" spans="1:7">
       <c r="A12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:7">
       <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="14" ht="67.5" customHeight="1" spans="1:7">
       <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="15" ht="27" customHeight="1" spans="1:7">
       <c r="A15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="16" ht="40.5" customHeight="1" spans="1:7">
       <c r="A16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="17" ht="40.5" customHeight="1" spans="1:6">
       <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A20" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1" spans="1:6">
+      <c r="A21" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1" spans="1:7">
-      <c r="A21" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="22" ht="40.5" customHeight="1" spans="1:6">
       <c r="A22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" ht="54" customHeight="1" spans="1:7">
+    </row>
+    <row r="23" ht="54" customHeight="1" spans="1:6">
       <c r="A23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" ht="54" customHeight="1" spans="1:7">
+    </row>
+    <row r="24" ht="54" customHeight="1" spans="1:6">
       <c r="A24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="25" ht="40.5" customHeight="1" spans="1:6">
       <c r="A25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A26" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1" spans="1:6">
+      <c r="A27" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" ht="27" customHeight="1" spans="1:7">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="28" ht="40.5" customHeight="1" spans="1:6">
       <c r="A28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A29" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1" spans="1:6">
+      <c r="A30" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" ht="54" customHeight="1" spans="1:7">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="31" ht="40.5" customHeight="1" spans="1:6">
       <c r="A31" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="32" ht="40.5" customHeight="1" spans="1:6">
       <c r="A32" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1" spans="1:6">
+      <c r="A33" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" ht="54" customHeight="1" spans="1:7">
-      <c r="A33" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A34" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A34" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" ht="27" customHeight="1" spans="1:7">
+    </row>
+    <row r="35" ht="27" customHeight="1" spans="1:6">
       <c r="A35" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" ht="27" customHeight="1" spans="1:6">
+      <c r="A36" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" ht="27" customHeight="1" spans="1:7">
-      <c r="A36" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" ht="54" customHeight="1" spans="1:6">
+      <c r="A37" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" ht="54" customHeight="1" spans="1:7">
-      <c r="A37" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" ht="27" customHeight="1" spans="1:7">
+    </row>
+    <row r="38" ht="27" customHeight="1" spans="1:6">
       <c r="A38" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" ht="27" customHeight="1" spans="1:6">
+      <c r="A39" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" ht="27" customHeight="1" spans="1:7">
-      <c r="A39" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" ht="54" customHeight="1" spans="1:7">
+    </row>
+    <row r="40" ht="54" customHeight="1" spans="1:6">
       <c r="A40" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" ht="27" customHeight="1" spans="1:7">
+    </row>
+    <row r="41" ht="27" customHeight="1" spans="1:6">
       <c r="A41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="F41" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A42" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A42" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" ht="54" customHeight="1" spans="1:7">
+    </row>
+    <row r="43" ht="54" customHeight="1" spans="1:6">
       <c r="A43" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" ht="67.5" customHeight="1" spans="1:6">
+      <c r="A44" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" ht="67.5" customHeight="1" spans="1:7">
-      <c r="A44" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A45" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A45" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A46" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A46" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" ht="27" customHeight="1" spans="1:6">
+      <c r="A47" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" ht="27" customHeight="1" spans="1:7">
-      <c r="A47" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" ht="67.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="48" ht="67.5" customHeight="1" spans="1:6">
       <c r="A48" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="49" ht="40.5" customHeight="1" spans="1:6">
       <c r="A49" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G49" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" ht="40.5" customHeight="1" spans="1:7">
+    </row>
+    <row r="50" ht="40.5" customHeight="1" spans="1:6">
       <c r="A50" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A51" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G50" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A52" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A52" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="F52" s="5" t="s">
+    </row>
+    <row r="53" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A53" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G52" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A53" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="54" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A54" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A54" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" ht="27" customHeight="1" spans="1:6">
+      <c r="A55" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G54" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" ht="27" customHeight="1" spans="1:7">
-      <c r="A55" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A56" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G55" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A56" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" ht="27" customHeight="1" spans="1:6">
+      <c r="A57" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G56" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" ht="27" customHeight="1" spans="1:7">
-      <c r="A57" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" ht="27" customHeight="1" spans="1:6">
+      <c r="A58" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" ht="27" customHeight="1" spans="1:7">
-      <c r="A58" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" ht="54" customHeight="1" spans="1:6">
+      <c r="A59" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" ht="54" customHeight="1" spans="1:7">
-      <c r="A59" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" ht="27" customHeight="1" spans="1:6">
+      <c r="A60" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G59" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" ht="27" customHeight="1" spans="1:7">
-      <c r="A60" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="61" ht="27" customHeight="1" spans="1:6">
+      <c r="A61" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G60" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" ht="27" customHeight="1" spans="1:7">
-      <c r="A61" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="F61" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" ht="27" customHeight="1" spans="1:6">
+      <c r="A62" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G61" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" ht="27" customHeight="1" spans="1:7">
-      <c r="A62" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" ht="27" customHeight="1" spans="1:6">
+      <c r="A63" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" ht="27" customHeight="1" spans="1:7">
-      <c r="A63" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="F63" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A64" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G63" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A64" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="F64" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A65" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F64" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G64" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A65" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="66" ht="40.5" customHeight="1" spans="1:6">
+      <c r="A66" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F65" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G65" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" ht="40.5" customHeight="1" spans="1:7">
-      <c r="A66" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="F66" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G66" t="s">
-        <v>13</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -3747,7 +3549,7 @@
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G66 G67:G2000">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G2000">
       <formula1>"pass,fail"</formula1>
     </dataValidation>
   </dataValidations>
